--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -26424,12 +26424,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26463,81 +26463,100 @@
         </is>
       </c>
       <c r="N152" t="n">
+        <v>16</v>
+      </c>
+      <c r="O152" t="n">
+        <v>16</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.1495180868525335</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
         <v>2</v>
       </c>
-      <c r="O152" t="n">
-        <v>2</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
-      <c r="AT152" t="n">
-        <v>0</v>
-      </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26564,17 +26583,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26608,81 +26627,175 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O153" t="n">
-        <v>12</v>
-      </c>
-      <c r="R153" t="n">
-        <v>0.003438045759323263</v>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE153" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF153" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG153" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH153" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM153" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN153" t="b">
+        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26714,12 +26827,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26744,7 +26857,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26753,13 +26866,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O154" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R154" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26792,42 +26905,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26889,7 +27002,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -26898,13 +27011,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O155" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R155" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.003438045759323263</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -27034,7 +27147,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -27043,13 +27156,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O156" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R156" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -27179,7 +27292,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -27188,13 +27301,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O157" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R157" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -27294,12 +27407,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27324,22 +27437,22 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27372,42 +27485,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27439,12 +27552,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27469,109 +27582,90 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N159" t="n">
+        <v>7</v>
+      </c>
+      <c r="O159" t="n">
+        <v>7</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
         <v>0</v>
       </c>
-      <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP159" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ159" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT159" t="n">
-        <v>2</v>
-      </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27598,17 +27692,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27647,170 +27741,76 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y160" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD160" t="inlineStr">
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE160" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF160" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG160" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH160" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI160" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ160" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM160" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN160" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP160" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT160" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV160" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27842,12 +27842,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27896,7 +27896,7 @@
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -27916,7 +27916,7 @@
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR161" t="inlineStr">
@@ -27926,7 +27926,7 @@
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT161" t="n">
@@ -27934,47 +27934,47 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28006,12 +28006,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28052,22 +28052,22 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="V162" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>Listeriose</t>
+          <t>Listeria</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -28127,17 +28127,17 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -28155,7 +28155,7 @@
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
@@ -28165,7 +28165,7 @@
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT162" t="n">
@@ -28173,45 +28173,448 @@
       </c>
       <c r="AU162" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ163" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT163" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV162" t="inlineStr">
+      <c r="AV163" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW162" t="inlineStr">
+      <c r="AW163" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX162" t="inlineStr">
+      <c r="AX163" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY162" t="inlineStr">
+      <c r="AY163" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ162" t="inlineStr">
+      <c r="AZ163" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA162" t="inlineStr">
+      <c r="BA163" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB162" t="inlineStr">
+      <c r="BB163" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC162" t="inlineStr">
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE164" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF164" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG164" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH164" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI164" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM164" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN164" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ164" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -28333,7 +28736,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -28343,7 +28746,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -28363,7 +28766,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -28395,7 +28798,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>552</v>
+        <v>568</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -28620,6 +28620,151 @@
         </is>
       </c>
     </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>5</v>
+      </c>
+      <c r="O165" t="n">
+        <v>5</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28653,7 +28798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -28736,7 +28881,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -28746,7 +28891,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -28798,7 +28943,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -22004,12 +22004,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22048,76 +22048,87 @@
       <c r="O126" t="n">
         <v>10</v>
       </c>
-      <c r="R126" t="n">
-        <v>0.1110149228479591</v>
-      </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22144,17 +22155,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22188,22 +22199,39 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O127" t="n">
-        <v>5</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.08894045854320688</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -22211,6 +22239,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary listeriosis notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -22218,70 +22304,65 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22308,17 +22389,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -22352,175 +22433,81 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O128" t="n">
-        <v>5</v>
-      </c>
-      <c r="U128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W128" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X128" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y128" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA128" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD128" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG128" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM128" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN128" t="b">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.1110149228479591</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ128" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR128" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS128" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -22552,12 +22539,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -22591,81 +22578,100 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R129" t="n">
-        <v>0.01355270280196709</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS129" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
       <c r="AT129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22692,17 +22698,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -22736,22 +22742,39 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O130" t="n">
-        <v>8</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0.1415180660636405</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Listeria</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -22759,6 +22782,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -22771,7 +22852,7 @@
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
@@ -22781,7 +22862,7 @@
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT130" t="n">
@@ -22789,47 +22870,47 @@
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22856,17 +22937,17 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -22900,175 +22981,81 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>8</v>
-      </c>
-      <c r="U131" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V131" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W131" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X131" t="inlineStr">
-        <is>
-          <t>Listeriose</t>
-        </is>
-      </c>
-      <c r="Y131" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA131" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD131" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG131" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN131" t="b">
         <v>1</v>
       </c>
+      <c r="R131" t="n">
+        <v>0.01355270280196709</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ131" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS131" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23100,12 +23087,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -23139,13 +23126,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R132" t="n">
-        <v>0.132388232653028</v>
+        <v>0.1415180660636405</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23154,7 +23141,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -23169,7 +23156,7 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
@@ -23177,57 +23164,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23259,12 +23251,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23298,29 +23290,29 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Listeriose</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -23330,7 +23322,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -23345,7 +23337,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -23380,17 +23372,17 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -23403,7 +23395,7 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
@@ -23411,57 +23403,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23493,12 +23490,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23532,13 +23529,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O134" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R134" t="n">
-        <v>0.1401732064242502</v>
+        <v>0.132388232653028</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23547,7 +23544,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -23562,7 +23559,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -23570,62 +23567,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23657,12 +23649,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23696,29 +23688,29 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="O135" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>Listeriainfektion</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -23728,7 +23720,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -23743,7 +23735,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -23778,17 +23770,17 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -23801,7 +23793,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
@@ -23809,62 +23801,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23896,12 +23883,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23935,81 +23922,100 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O136" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R136" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.1401732064242502</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24036,17 +24042,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -24071,7 +24077,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -24080,81 +24086,175 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O137" t="n">
-        <v>6</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24186,12 +24286,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24216,7 +24316,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -24225,13 +24325,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O138" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R138" t="n">
-        <v>0.00401105338587714</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24264,42 +24364,42 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24361,7 +24461,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24370,13 +24470,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O139" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R139" t="n">
-        <v>0.002292030506215508</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -24506,7 +24606,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24621,12 +24721,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24651,22 +24751,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O141" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R141" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.002292030506215508</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -24699,42 +24799,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24766,12 +24866,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24796,23 +24896,26 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.00401105338587714</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -24841,42 +24944,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24908,12 +25011,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24947,14 +25050,17 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.01836405909759895</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -24988,12 +25094,12 @@
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -25008,12 +25114,12 @@
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
@@ -25050,12 +25156,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -25130,7 +25236,7 @@
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
@@ -25150,7 +25256,7 @@
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
@@ -25192,12 +25298,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25272,7 +25378,7 @@
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
@@ -25292,7 +25398,7 @@
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
@@ -25334,12 +25440,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25414,7 +25520,7 @@
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
@@ -25434,7 +25540,7 @@
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
@@ -25476,12 +25582,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25556,7 +25662,7 @@
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
@@ -25576,7 +25682,7 @@
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
@@ -25618,12 +25724,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25657,100 +25763,78 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>2</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA148" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ148" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -25777,17 +25861,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25821,175 +25905,78 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>2</v>
-      </c>
-      <c r="U149" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V149" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W149" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X149" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y149" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA149" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD149" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE149" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF149" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG149" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ149" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM149" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN149" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP149" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ149" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT149" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV149" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26021,12 +26008,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26060,13 +26047,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O150" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R150" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26075,7 +26062,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -26095,7 +26082,7 @@
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
@@ -26105,7 +26092,7 @@
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -26113,47 +26100,47 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26185,12 +26172,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -26224,29 +26211,29 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O151" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Listeriose</t>
+          <t>Listeria</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
@@ -26271,7 +26258,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -26306,17 +26293,17 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN151" t="b">
@@ -26334,7 +26321,7 @@
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
@@ -26344,7 +26331,7 @@
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT151" t="n">
@@ -26352,47 +26339,47 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26424,12 +26411,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26463,13 +26450,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O152" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1495180868525335</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26478,7 +26465,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -26508,7 +26495,7 @@
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -26521,42 +26508,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26588,12 +26575,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26627,29 +26614,29 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O153" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Listeriainfektion</t>
+          <t>Listeriose</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -26674,7 +26661,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -26709,17 +26696,17 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -26747,7 +26734,7 @@
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT153" t="n">
@@ -26760,42 +26747,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26827,12 +26814,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26866,81 +26853,100 @@
         </is>
       </c>
       <c r="N154" t="n">
+        <v>16</v>
+      </c>
+      <c r="O154" t="n">
+        <v>16</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.1495180868525335</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
         <v>2</v>
       </c>
-      <c r="O154" t="n">
-        <v>2</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP154" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr"/>
-      <c r="AT154" t="n">
-        <v>0</v>
-      </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26967,17 +26973,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27011,81 +27017,175 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O155" t="n">
-        <v>12</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0.003438045759323263</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27117,12 +27217,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27147,7 +27247,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -27156,13 +27256,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R156" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -27195,42 +27295,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27292,7 +27392,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -27301,13 +27401,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O157" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R157" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.003438045759323263</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -27437,7 +27537,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -27446,13 +27546,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O158" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R158" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27582,7 +27682,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27591,13 +27691,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O159" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R159" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27697,12 +27797,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27727,22 +27827,22 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O160" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27775,42 +27875,42 @@
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27842,12 +27942,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27872,109 +27972,90 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N161" t="n">
+        <v>7</v>
+      </c>
+      <c r="O161" t="n">
+        <v>7</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
         <v>0</v>
       </c>
-      <c r="O161" t="n">
-        <v>0</v>
-      </c>
-      <c r="R161" t="n">
-        <v>0</v>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA161" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP161" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ161" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT161" t="n">
-        <v>2</v>
-      </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28001,17 +28082,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28050,170 +28131,76 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="U162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y162" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA162" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD162" t="inlineStr">
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE162" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF162" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG162" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH162" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI162" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ162" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM162" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN162" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP162" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ162" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT162" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV162" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28245,12 +28232,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28299,7 +28286,7 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -28319,7 +28306,7 @@
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
@@ -28329,7 +28316,7 @@
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT163" t="n">
@@ -28337,47 +28324,47 @@
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28409,12 +28396,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28455,22 +28442,22 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="V164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>Listeriose</t>
+          <t>Listeria</t>
         </is>
       </c>
       <c r="Y164" t="inlineStr">
@@ -28495,7 +28482,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -28530,17 +28517,17 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -28558,7 +28545,7 @@
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR164" t="inlineStr">
@@ -28568,7 +28555,7 @@
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -28576,47 +28563,47 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28648,118 +28635,521 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ165" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT165" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="G167" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>D108</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Listeriosis</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
         <is>
           <t>李斯特菌病</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N165" t="n">
+      <c r="N167" t="n">
         <v>5</v>
       </c>
-      <c r="O165" t="n">
+      <c r="O167" t="n">
         <v>5</v>
       </c>
-      <c r="R165" t="n">
+      <c r="R167" t="n">
         <v>0.001432519066384693</v>
       </c>
-      <c r="S165" t="inlineStr">
+      <c r="S167" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO165" t="inlineStr">
+      <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP165" t="inlineStr">
+      <c r="AP167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR165" t="inlineStr">
+      <c r="AR167" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS165" t="inlineStr"/>
-      <c r="AT165" t="n">
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
         <v>0</v>
       </c>
-      <c r="AU165" t="inlineStr">
+      <c r="AU167" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV165" t="inlineStr">
+      <c r="AV167" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW165" t="inlineStr">
+      <c r="AW167" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX165" t="inlineStr">
+      <c r="AX167" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY165" t="inlineStr">
+      <c r="AY167" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ165" t="inlineStr">
+      <c r="AZ167" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA165" t="inlineStr">
+      <c r="BA167" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB165" t="inlineStr">
+      <c r="BB167" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC165" t="inlineStr">
+      <c r="BC167" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -28881,7 +29271,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -28891,7 +29281,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -28911,7 +29301,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -28943,7 +29333,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>573</v>
+        <v>583</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -26814,12 +26814,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26853,13 +26853,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O154" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="R154" t="n">
-        <v>0.1495180868525335</v>
+        <v>0.05673781399415487</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -26883,7 +26883,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
@@ -26891,62 +26891,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26978,12 +26973,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27017,29 +27012,29 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O155" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>Listeriainfektion</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -27049,7 +27044,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -27064,7 +27059,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -27099,17 +27094,17 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN155" t="b">
@@ -27122,7 +27117,7 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
@@ -27130,62 +27125,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27217,12 +27207,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27256,81 +27246,100 @@
         </is>
       </c>
       <c r="N156" t="n">
+        <v>16</v>
+      </c>
+      <c r="O156" t="n">
+        <v>16</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.1495180868525335</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
         <v>2</v>
       </c>
-      <c r="O156" t="n">
-        <v>2</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP156" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
-      <c r="AT156" t="n">
-        <v>0</v>
-      </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27357,17 +27366,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -27401,81 +27410,175 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O157" t="n">
-        <v>12</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0.003438045759323263</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27507,12 +27610,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27537,7 +27640,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -27546,13 +27649,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R158" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27585,42 +27688,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27682,7 +27785,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27691,13 +27794,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O159" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R159" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.003438045759323263</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27827,7 +27930,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -27836,13 +27939,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O160" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R160" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27972,7 +28075,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -27981,13 +28084,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O161" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R161" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -28087,12 +28190,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28117,22 +28220,22 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O162" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -28165,42 +28268,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28232,12 +28335,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -28262,109 +28365,90 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N163" t="n">
+        <v>7</v>
+      </c>
+      <c r="O163" t="n">
+        <v>7</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
         <v>0</v>
       </c>
-      <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="R163" t="n">
-        <v>0</v>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP163" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT163" t="n">
-        <v>2</v>
-      </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28391,17 +28475,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28440,170 +28524,76 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT164" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV164" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28635,12 +28625,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28689,7 +28679,7 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -28709,7 +28699,7 @@
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
@@ -28719,7 +28709,7 @@
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT165" t="n">
@@ -28727,47 +28717,47 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28799,12 +28789,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28845,22 +28835,22 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="V166" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>Listeriose</t>
+          <t>Listeria</t>
         </is>
       </c>
       <c r="Y166" t="inlineStr">
@@ -28885,7 +28875,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -28920,17 +28910,17 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN166" t="b">
@@ -28948,7 +28938,7 @@
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
@@ -28958,7 +28948,7 @@
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT166" t="n">
@@ -28966,47 +28956,47 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29038,118 +29028,521 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD168" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE168" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF168" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG168" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH168" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI168" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM168" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN168" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO168" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP168" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ168" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR168" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS168" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU168" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA168" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB168" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC168" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="G169" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>D108</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Listeriosis</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
         <is>
           <t>李斯特菌病</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N167" t="n">
+      <c r="N169" t="n">
         <v>5</v>
       </c>
-      <c r="O167" t="n">
+      <c r="O169" t="n">
         <v>5</v>
       </c>
-      <c r="R167" t="n">
+      <c r="R169" t="n">
         <v>0.001432519066384693</v>
       </c>
-      <c r="S167" t="inlineStr">
+      <c r="S169" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO167" t="inlineStr">
+      <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP167" t="inlineStr">
+      <c r="AP169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR167" t="inlineStr">
+      <c r="AR169" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS167" t="inlineStr"/>
-      <c r="AT167" t="n">
+      <c r="AS169" t="inlineStr"/>
+      <c r="AT169" t="n">
         <v>0</v>
       </c>
-      <c r="AU167" t="inlineStr">
+      <c r="AU169" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV167" t="inlineStr">
+      <c r="AV169" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW167" t="inlineStr">
+      <c r="AW169" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX167" t="inlineStr">
+      <c r="AX169" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY167" t="inlineStr">
+      <c r="AY169" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ167" t="inlineStr">
+      <c r="AZ169" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA167" t="inlineStr">
+      <c r="BA169" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB167" t="inlineStr">
+      <c r="BB169" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC167" t="inlineStr">
+      <c r="BC169" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -29271,7 +29664,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10">
@@ -29281,7 +29674,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -29301,7 +29694,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -29333,7 +29726,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -29067,13 +29067,13 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
@@ -29231,10 +29231,10 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
@@ -29726,7 +29726,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -29548,6 +29548,151 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N170" t="n">
+        <v>7</v>
+      </c>
+      <c r="O170" t="n">
+        <v>7</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV170" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA170" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB170" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC170" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29581,7 +29726,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -29664,7 +29809,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -29674,7 +29819,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">
@@ -29726,7 +29871,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -26411,12 +26411,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26450,100 +26450,81 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>0.08844879128977531</v>
+        <v>0</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26570,7 +26551,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -26619,98 +26600,23 @@
       <c r="O153" t="n">
         <v>5</v>
       </c>
+      <c r="R153" t="n">
+        <v>0.08844879128977531</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U153" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
-      <c r="V153" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W153" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X153" t="inlineStr">
-        <is>
-          <t>Listeriose</t>
-        </is>
-      </c>
-      <c r="Y153" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD153" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE153" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF153" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG153" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH153" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ153" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM153" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN153" t="b">
-        <v>1</v>
       </c>
       <c r="AO153" t="inlineStr">
         <is>
@@ -26809,17 +26715,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26853,22 +26759,39 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O154" t="n">
-        <v>3</v>
-      </c>
-      <c r="R154" t="n">
-        <v>0.05673781399415487</v>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -26876,6 +26799,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>1</v>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -26883,7 +26864,7 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
@@ -26891,57 +26872,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26968,7 +26954,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -27017,98 +27003,23 @@
       <c r="O155" t="n">
         <v>3</v>
       </c>
+      <c r="R155" t="n">
+        <v>0.05673781399415487</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U155" t="inlineStr">
         <is>
           <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Listeriosis</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN155" t="b">
-        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
@@ -27202,17 +27113,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -27246,22 +27157,39 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O156" t="n">
-        <v>16</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0.1495180868525335</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -27269,6 +27197,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>1</v>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27276,7 +27262,7 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
@@ -27284,62 +27270,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27366,7 +27347,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -27415,98 +27396,23 @@
       <c r="O157" t="n">
         <v>16</v>
       </c>
+      <c r="R157" t="n">
+        <v>0.1495180868525335</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Listeriainfektion</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -27605,17 +27511,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27649,81 +27555,175 @@
         </is>
       </c>
       <c r="N158" t="n">
+        <v>16</v>
+      </c>
+      <c r="O158" t="n">
+        <v>16</v>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AT158" t="n">
         <v>2</v>
       </c>
-      <c r="O158" t="n">
-        <v>2</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP158" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
-      <c r="AT158" t="n">
-        <v>0</v>
-      </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27755,12 +27755,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27794,13 +27794,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R159" t="n">
-        <v>0.003438045759323263</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27833,42 +27833,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27930,7 +27930,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -27939,13 +27939,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O160" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R160" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.003438045759323263</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -28075,7 +28075,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -28084,13 +28084,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O161" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="R161" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -28229,13 +28229,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O162" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R162" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -28365,7 +28365,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -28374,13 +28374,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O163" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R163" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -28480,12 +28480,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28510,22 +28510,22 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O164" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R164" t="n">
-        <v>0</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28558,42 +28558,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28625,12 +28625,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28677,87 +28677,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AA165" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ165" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR165" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS165" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28784,7 +28765,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -28828,103 +28809,28 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O166" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U166" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
-      <c r="V166" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y166" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD166" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE166" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF166" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG166" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH166" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI166" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN166" t="b">
-        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
@@ -29023,17 +28929,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -29072,17 +28978,34 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
-      <c r="R167" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Listeria</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -29090,6 +29013,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -29102,7 +29083,7 @@
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
@@ -29112,7 +29093,7 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT167" t="n">
@@ -29120,47 +29101,47 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29187,7 +29168,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -29231,103 +29212,28 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O168" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0.03537951651591013</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U168" t="inlineStr">
         <is>
           <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>Listeriose</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN168" t="b">
-        <v>1</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -29426,17 +29332,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -29461,7 +29367,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -29470,81 +29376,175 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O169" t="n">
-        <v>5</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0.001432519066384693</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -29615,13 +29615,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O170" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R170" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.001432519066384693</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -29688,6 +29688,296 @@
         </is>
       </c>
       <c r="BC170" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N171" t="n">
+        <v>7</v>
+      </c>
+      <c r="O171" t="n">
+        <v>7</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP171" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR171" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr"/>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV171" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA171" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB171" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC171" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>10</v>
+      </c>
+      <c r="O172" t="n">
+        <v>10</v>
+      </c>
+      <c r="R172" t="n">
+        <v>0.002865038132769385</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR172" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr"/>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -29726,7 +30016,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -29809,7 +30099,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -29819,7 +30109,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -29871,7 +30161,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>594</v>
+        <v>606</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -28664,13 +28664,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>0.01101843545855937</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28809,13 +28809,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R166" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -28973,10 +28973,10 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
@@ -29980,6 +29980,554 @@
       <c r="BC172" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N173" t="n">
+        <v>5</v>
+      </c>
+      <c r="O173" t="n">
+        <v>5</v>
+      </c>
+      <c r="R173" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP173" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR173" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr"/>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV173" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0</v>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR174" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS174" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="AT174" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU174" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV174" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB174" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC174" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Listeria</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD175" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE175" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF175" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG175" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH175" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI175" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
+        </is>
+      </c>
+      <c r="AM175" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN175" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP175" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ175" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR175" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS175" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="AT175" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU175" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV175" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA175" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB175" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC175" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -30099,7 +30647,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -30109,7 +30657,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -30129,7 +30677,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -30161,7 +30709,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>606</v>
+        <v>615</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -2247,7 +2247,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -29468,7 +29468,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN169" t="b">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1347,6 +1367,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1483,6 +1508,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1628,6 +1658,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1764,6 +1799,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1900,6 +1940,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2983,6 +3028,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3371,7 +3421,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4333,6 +4383,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4481,6 +4536,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4629,6 +4689,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4777,6 +4842,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4925,6 +4995,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5073,6 +5148,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5221,6 +5301,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5366,6 +5451,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5502,6 +5592,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5647,6 +5742,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5783,6 +5883,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5928,6 +6033,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6073,6 +6183,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6218,6 +6333,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6354,6 +6474,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7437,6 +7562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7825,7 +7955,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -8787,6 +8917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8935,6 +9070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9083,6 +9223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9231,6 +9376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9379,6 +9529,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9527,6 +9682,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9672,6 +9832,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9817,6 +9982,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9962,6 +10132,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10098,6 +10273,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10243,6 +10423,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10388,6 +10573,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10524,6 +10714,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10660,6 +10855,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11743,6 +11943,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12131,7 +12336,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -13093,6 +13298,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13241,6 +13451,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13389,6 +13604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13537,6 +13757,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13685,6 +13910,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13830,6 +14060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13975,6 +14210,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14111,6 +14351,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14256,6 +14501,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14401,6 +14651,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14537,6 +14792,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14682,6 +14942,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14818,6 +15083,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14963,6 +15233,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16046,6 +16321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16434,7 +16714,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -17390,6 +17670,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17538,6 +17823,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17686,6 +17976,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17834,6 +18129,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17982,6 +18282,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18127,6 +18432,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18272,6 +18582,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18408,6 +18723,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18553,6 +18873,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18698,6 +19023,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18843,6 +19173,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18979,6 +19314,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19115,6 +19455,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19251,6 +19596,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20334,6 +20684,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20722,7 +21077,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -21678,6 +22033,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21826,6 +22186,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21974,6 +22339,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22122,6 +22492,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22270,6 +22645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22415,6 +22795,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22560,6 +22945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22705,6 +23095,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22850,6 +23245,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22995,6 +23395,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23140,6 +23545,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23285,6 +23695,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23430,6 +23845,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23566,6 +23986,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23702,6 +24127,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24785,6 +25215,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25173,7 +25608,7 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN150" t="b">
@@ -26129,6 +26564,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26274,6 +26714,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26419,6 +26864,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26564,6 +27014,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26709,6 +27164,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26854,6 +27314,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26999,6 +27464,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27144,6 +27614,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27289,6 +27764,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27425,6 +27905,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27570,6 +28055,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27706,6 +28196,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27842,6 +28337,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27987,6 +28487,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28119,10 +28624,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O169" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -28275,10 +28780,10 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O170" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
@@ -29070,6 +29575,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29458,7 +29968,7 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN176" t="b">
@@ -30414,6 +30924,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30559,6 +31074,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30704,6 +31224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30849,6 +31374,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30994,6 +31524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31139,6 +31674,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31284,6 +31824,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31420,6 +31965,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31565,6 +32115,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31710,6 +32265,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31855,6 +32415,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32000,6 +32565,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32145,6 +32715,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32281,6 +32856,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32374,12 +32954,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -32413,22 +32993,19 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O195" t="n">
-        <v>2</v>
-      </c>
-      <c r="R195" t="n">
-        <v>0.03557618341728275</v>
+        <v>12</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -32443,70 +33020,65 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32538,12 +33110,12 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -32577,29 +33149,29 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O196" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>Listeria</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="Y196" t="inlineStr">
@@ -32609,7 +33181,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -32624,7 +33196,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -32659,17 +33231,17 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
+          <t>PHO IDTO current-year monthly preliminary listeriosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN196" t="b">
@@ -32682,70 +33254,65 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_CA_ON_PHO_IDTO_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA196" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB196" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC196" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32777,12 +33344,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -32816,13 +33383,13 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>0.05550746142397953</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
@@ -32855,42 +33422,42 @@
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -32922,12 +33489,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -32961,13 +33528,13 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O198" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R198" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -32976,7 +33543,7 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -32996,7 +33563,7 @@
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
@@ -33006,7 +33573,7 @@
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT198" t="n">
@@ -33014,47 +33581,47 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33086,12 +33653,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -33125,29 +33692,29 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O199" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="V199" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>Listeriose</t>
+          <t>Listeria</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -33172,7 +33739,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -33207,17 +33774,17 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -33235,7 +33802,7 @@
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
@@ -33245,7 +33812,7 @@
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT199" t="n">
@@ -33253,47 +33820,47 @@
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33325,12 +33892,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -33364,24 +33931,19 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
-        <v>0.05673781399415487</v>
+        <v>0</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
-        <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33389,70 +33951,66 @@
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ200" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS200" t="inlineStr">
-        <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR200" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -33479,17 +34037,17 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -33523,39 +34081,22 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O201" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="R201" t="n">
+        <v>0.08844879128977531</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U201" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V201" t="inlineStr">
-        <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W201" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>Listeriosis</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -33563,64 +34104,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD201" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE201" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF201" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG201" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH201" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI201" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ201" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
-        </is>
-      </c>
-      <c r="AM201" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN201" t="b">
-        <v>1</v>
-      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33628,7 +34111,7 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
@@ -33636,57 +34119,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR201" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33713,17 +34201,17 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -33757,22 +34245,39 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O202" t="n">
-        <v>16</v>
-      </c>
-      <c r="R202" t="n">
-        <v>0.1495180868525335</v>
-      </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W202" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y202" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -33780,6 +34285,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD202" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE202" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF202" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG202" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH202" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI202" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM202" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN202" t="b">
+        <v>1</v>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -33802,7 +34365,7 @@
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT202" t="n">
@@ -33815,42 +34378,42 @@
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33877,17 +34440,17 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -33921,39 +34484,22 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O203" t="n">
-        <v>16</v>
+        <v>3</v>
+      </c>
+      <c r="R203" t="n">
+        <v>0.05673781399415487</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
-        </is>
-      </c>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
-        </is>
-      </c>
-      <c r="W203" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X203" t="inlineStr">
-        <is>
-          <t>Listeriainfektion</t>
-        </is>
-      </c>
-      <c r="Y203" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -33961,135 +34507,72 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD203" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE203" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF203" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG203" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH203" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI203" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ203" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM203" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN203" t="b">
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
         <v>1</v>
       </c>
-      <c r="AO203" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP203" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ203" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS203" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
-        </is>
-      </c>
-      <c r="AT203" t="n">
-        <v>2</v>
-      </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34116,17 +34599,17 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -34160,81 +34643,170 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O204" t="n">
-        <v>2</v>
-      </c>
-      <c r="R204" t="n">
-        <v>0.008691384892873792</v>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X204" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD204" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE204" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF204" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG204" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH204" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI204" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly listeriosis notifications.</t>
+        </is>
+      </c>
+      <c r="AM204" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN204" t="b">
+        <v>1</v>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS204" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ204" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS204" t="inlineStr">
+        <is>
+          <t>SER_NZ_LISTERIOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34266,12 +34838,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -34305,81 +34877,100 @@
         </is>
       </c>
       <c r="N205" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O205" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R205" t="n">
-        <v>0.003438045759323263</v>
+        <v>0.1495180868525335</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ205" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR205" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS205" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS205" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU205" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV205" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA205" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB205" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC205" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34406,17 +34997,17 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -34441,7 +35032,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
@@ -34450,81 +35041,175 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="O206" t="n">
-        <v>3</v>
-      </c>
-      <c r="R206" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>16</v>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD206" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE206" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF206" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG206" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH206" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI206" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM206" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN206" t="b">
+        <v>1</v>
       </c>
       <c r="AO206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ206" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR206" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS206" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS206" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU206" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV206" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA206" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB206" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC206" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34556,12 +35241,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -34586,7 +35271,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
@@ -34595,17 +35280,22 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="O207" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R207" t="n">
-        <v>0.003724549572600201</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -34634,42 +35324,42 @@
       </c>
       <c r="AV207" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA207" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB207" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC207" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -34731,7 +35421,7 @@
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
@@ -34740,17 +35430,22 @@
         </is>
       </c>
       <c r="N208" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O208" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R208" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.003438045759323263</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -34876,7 +35571,7 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
@@ -34885,17 +35580,22 @@
         </is>
       </c>
       <c r="N209" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O209" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R209" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -34991,12 +35691,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -35021,26 +35721,31 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N210" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="O210" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R210" t="n">
-        <v>0.01101843545855937</v>
+        <v>0.003724549572600201</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -35069,42 +35774,42 @@
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35136,12 +35841,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -35166,26 +35871,31 @@
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -35214,42 +35924,42 @@
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35281,12 +35991,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -35311,26 +36021,31 @@
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O212" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R212" t="n">
-        <v>0</v>
+        <v>0.00200552669293857</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -35359,42 +36074,42 @@
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35426,12 +36141,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -35465,17 +36180,22 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O213" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>0.01101843545855937</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -35509,12 +36229,12 @@
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
@@ -35529,12 +36249,12 @@
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
@@ -35571,12 +36291,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -35621,6 +36341,11 @@
       <c r="S214" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -35654,7 +36379,7 @@
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
@@ -35674,7 +36399,7 @@
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
@@ -35716,12 +36441,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -35766,6 +36491,11 @@
       <c r="S215" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -35799,7 +36529,7 @@
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
@@ -35819,7 +36549,7 @@
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
@@ -35861,12 +36591,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -35911,6 +36641,11 @@
       <c r="S216" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -35944,7 +36679,7 @@
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
@@ -35964,7 +36699,7 @@
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
@@ -36006,12 +36741,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -36044,9 +36779,23 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0</v>
+      </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -36080,7 +36829,7 @@
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
@@ -36100,7 +36849,7 @@
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
@@ -36142,12 +36891,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -36192,6 +36941,11 @@
       <c r="S218" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -36225,7 +36979,7 @@
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
@@ -36245,7 +36999,7 @@
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
@@ -36287,12 +37041,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -36326,22 +37080,17 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R219" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U219" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -36351,75 +37100,66 @@
       </c>
       <c r="AO219" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ219" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR219" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS219" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36446,17 +37186,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -36489,40 +37229,9 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N220" t="n">
-        <v>2</v>
-      </c>
-      <c r="O220" t="n">
-        <v>2</v>
-      </c>
-      <c r="U220" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="V220" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X220" t="inlineStr">
-        <is>
-          <t>Listeria</t>
-        </is>
-      </c>
-      <c r="Y220" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z220" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -36530,135 +37239,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB220" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD220" t="inlineStr">
+      <c r="AO220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP220" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR220" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr"/>
+      <c r="AT220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU220" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV220" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE220" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF220" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG220" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH220" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI220" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ220" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
-        </is>
-      </c>
-      <c r="AM220" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN220" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP220" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ220" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
-      <c r="AT220" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV220" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36690,12 +37332,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -36729,22 +37371,17 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -36754,75 +37391,66 @@
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ221" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36849,17 +37477,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -36898,34 +37526,17 @@
       <c r="O222" t="n">
         <v>2</v>
       </c>
+      <c r="R222" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V222" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W222" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X222" t="inlineStr">
-        <is>
-          <t>Listeriose</t>
-        </is>
-      </c>
-      <c r="Y222" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z222" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -36933,64 +37544,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB222" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD222" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE222" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF222" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG222" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH222" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI222" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ222" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK222" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM222" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN222" t="b">
-        <v>1</v>
-      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37003,7 +37556,7 @@
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
@@ -37013,7 +37566,7 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -37021,47 +37574,47 @@
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37088,17 +37641,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -37123,7 +37676,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -37132,81 +37685,175 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O223" t="n">
-        <v>5</v>
-      </c>
-      <c r="R223" t="n">
-        <v>0.001432519066384693</v>
-      </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X223" t="inlineStr">
+        <is>
+          <t>Listeria</t>
+        </is>
+      </c>
+      <c r="Y223" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z223" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC223" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD223" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE223" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF223" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG223" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH223" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI223" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ223" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
+        </is>
+      </c>
+      <c r="AM223" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN223" t="b">
+        <v>1</v>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ223" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS223" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
       <c r="AT223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37238,12 +37885,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -37268,7 +37915,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -37277,81 +37924,100 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O224" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R224" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ224" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR224" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS224" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU224" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37378,17 +38044,17 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -37413,7 +38079,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -37422,81 +38088,175 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O225" t="n">
-        <v>10</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.002865038132769385</v>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD225" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE225" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF225" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG225" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH225" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI225" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ225" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM225" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN225" t="b">
+        <v>1</v>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR225" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37528,12 +38288,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -37558,7 +38318,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -37567,81 +38327,100 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O226" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R226" t="n">
-        <v>0.001432519066384693</v>
+        <v>0.09344880428283346</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ226" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS226" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
       <c r="AT226" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -37668,17 +38447,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -37703,31 +38482,48 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O227" t="n">
-        <v>0</v>
-      </c>
-      <c r="R227" t="n">
-        <v>0</v>
-      </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
+        </is>
+      </c>
+      <c r="W227" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X227" t="inlineStr">
+        <is>
+          <t>Listeriainfektion</t>
+        </is>
+      </c>
+      <c r="Y227" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -37735,6 +38531,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC227" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD227" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE227" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF227" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG227" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH227" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI227" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ227" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM227" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN227" t="b">
+        <v>1</v>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -37747,7 +38601,7 @@
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
@@ -37757,7 +38611,7 @@
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_210</t>
+          <t>SER_SE_FOHM_SMINET_LISTERIOSIS</t>
         </is>
       </c>
       <c r="AT227" t="n">
@@ -37765,47 +38619,47 @@
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -37832,219 +38686,1536 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>5</v>
+      </c>
+      <c r="O228" t="n">
+        <v>5</v>
+      </c>
+      <c r="R228" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
+      <c r="AT228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>7</v>
+      </c>
+      <c r="O229" t="n">
+        <v>7</v>
+      </c>
+      <c r="R229" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr"/>
+      <c r="AT229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>10</v>
+      </c>
+      <c r="O230" t="n">
+        <v>10</v>
+      </c>
+      <c r="R230" t="n">
+        <v>0.002865038132769385</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
+      <c r="AT230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>5</v>
+      </c>
+      <c r="O231" t="n">
+        <v>5</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.001432519066384693</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
+      <c r="AT231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ232" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_210</t>
+        </is>
+      </c>
+      <c r="AT232" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G233" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>D108</t>
-        </is>
-      </c>
-      <c r="I228" t="inlineStr">
-        <is>
-          <t>Listeriosis</t>
-        </is>
-      </c>
-      <c r="J228" t="inlineStr">
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
         <is>
           <t>李斯特菌病</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="K233" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="L233" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M228" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N228" t="n">
+      <c r="N233" t="n">
         <v>0</v>
       </c>
-      <c r="O228" t="n">
+      <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="U233" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
-      <c r="V228" t="inlineStr">
+      <c r="V233" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
-      <c r="W228" t="inlineStr">
+      <c r="W233" t="inlineStr">
         <is>
           <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
-      <c r="X228" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>Listeria</t>
         </is>
       </c>
-      <c r="Y228" t="inlineStr">
+      <c r="Y233" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z228" t="inlineStr">
+      <c r="Z233" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA228" t="inlineStr">
+      <c r="AA233" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB228" t="inlineStr">
+      <c r="AB233" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC228" t="inlineStr">
+      <c r="AC233" t="inlineStr">
         <is>
           <t>country:FI:national</t>
         </is>
       </c>
-      <c r="AD228" t="inlineStr">
+      <c r="AD233" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE228" t="inlineStr">
+      <c r="AE233" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF228" t="inlineStr">
+      <c r="AF233" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG228" t="inlineStr">
+      <c r="AG233" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH228" t="inlineStr">
+      <c r="AH233" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI228" t="inlineStr">
+      <c r="AI233" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ228" t="inlineStr">
+      <c r="AJ233" t="inlineStr">
         <is>
           <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
-      <c r="AK228" t="inlineStr">
+      <c r="AK233" t="inlineStr">
         <is>
           <t>Finland THL national monthly notification series; THL reporting group code 210.</t>
         </is>
       </c>
-      <c r="AM228" t="inlineStr">
+      <c r="AM233" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN228" t="b">
+      <c r="AN233" t="b">
         <v>1</v>
       </c>
-      <c r="AO228" t="inlineStr">
+      <c r="AO233" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP228" t="inlineStr">
+      <c r="AP233" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ228" t="inlineStr">
+      <c r="AQ233" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR228" t="inlineStr">
+      <c r="AR233" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS228" t="inlineStr">
+      <c r="AS233" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
-      <c r="AT228" t="n">
+      <c r="AT233" t="n">
         <v>2</v>
       </c>
-      <c r="AU228" t="inlineStr">
+      <c r="AU233" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV228" t="inlineStr">
+      <c r="AV233" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW228" t="inlineStr">
+      <c r="AW233" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX228" t="inlineStr">
+      <c r="AX233" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY228" t="inlineStr">
+      <c r="AY233" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ228" t="inlineStr">
+      <c r="AZ233" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA228" t="inlineStr">
+      <c r="BA233" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB228" t="inlineStr">
+      <c r="BB233" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC228" t="inlineStr">
+      <c r="BC233" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ234" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT234" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X235" t="inlineStr">
+        <is>
+          <t>Listeriose</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC235" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD235" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE235" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF235" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG235" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH235" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI235" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ235" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM235" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN235" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ235" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_306_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT235" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>11</v>
+      </c>
+      <c r="O236" t="n">
+        <v>11</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.003151541946046324</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
+      <c r="AT236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38081,7 +40252,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -38164,7 +40335,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -38174,7 +40345,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>227</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -38194,7 +40365,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -38226,7 +40397,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>625</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -39330,13 +39330,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -39494,10 +39494,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -39330,13 +39330,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R232" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -39494,10 +39494,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -4678,9 +4678,6 @@
       <c r="O25" t="n">
         <v>8</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.002292030506215508</v>
       </c>
@@ -4831,9 +4828,6 @@
       <c r="O26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -4984,9 +4978,6 @@
       <c r="O27" t="n">
         <v>3</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -5137,9 +5128,6 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -9059,9 +9047,6 @@
       <c r="O51" t="n">
         <v>4</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -9212,9 +9197,6 @@
       <c r="O52" t="n">
         <v>5</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -9365,9 +9347,6 @@
       <c r="O53" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -9518,9 +9497,6 @@
       <c r="O54" t="n">
         <v>4</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -13440,9 +13416,6 @@
       <c r="O77" t="n">
         <v>4</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -13593,9 +13566,6 @@
       <c r="O78" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -13746,9 +13716,6 @@
       <c r="O79" t="n">
         <v>7</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -13899,9 +13866,6 @@
       <c r="O80" t="n">
         <v>4</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -17812,9 +17776,6 @@
       <c r="O103" t="n">
         <v>3</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -17965,9 +17926,6 @@
       <c r="O104" t="n">
         <v>4</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -18118,9 +18076,6 @@
       <c r="O105" t="n">
         <v>3</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -18271,9 +18226,6 @@
       <c r="O106" t="n">
         <v>5</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.001432519066384693</v>
       </c>
@@ -22175,9 +22127,6 @@
       <c r="O129" t="n">
         <v>4</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.001146015253107754</v>
       </c>
@@ -22328,9 +22277,6 @@
       <c r="O130" t="n">
         <v>2</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -22481,9 +22427,6 @@
       <c r="O131" t="n">
         <v>10</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.002865038132769385</v>
       </c>
@@ -22634,9 +22577,6 @@
       <c r="O132" t="n">
         <v>3</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -40214,6 +40154,156 @@
         </is>
       </c>
       <c r="BC236" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>7</v>
+      </c>
+      <c r="O237" t="n">
+        <v>7</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -40252,7 +40342,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -40335,7 +40425,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
@@ -40345,7 +40435,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -40397,7 +40487,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>668</v>
+        <v>675</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -89400,6 +89400,150 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N636" t="n">
+        <v>14</v>
+      </c>
+      <c r="O636" t="n">
+        <v>14</v>
+      </c>
+      <c r="R636" t="n">
+        <v>0.01673755059193663</v>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+        </is>
+      </c>
+      <c r="AA636" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO636" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP636" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS636" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+        </is>
+      </c>
+      <c r="AT636" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV636" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW636" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX636" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY636" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ636" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA636" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB636" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC636" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -89433,7 +89577,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -89516,7 +89660,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="10">
@@ -89526,7 +89670,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="11">
@@ -89578,7 +89722,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1073</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d108/2026-2029.xlsx
+++ b/diseases/d108/2026-2029.xlsx
@@ -78772,13 +78772,13 @@
         </is>
       </c>
       <c r="N560" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O560" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R560" t="n">
-        <v>0.01101843545855937</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="AA560" t="inlineStr">
         <is>
@@ -87157,12 +87157,12 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -87196,18 +87196,13 @@
         </is>
       </c>
       <c r="N620" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O620" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R620" t="n">
-        <v>0.05336427512592412</v>
-      </c>
-      <c r="U620" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
+        <v>0.00367281181951979</v>
       </c>
       <c r="AA620" t="inlineStr">
         <is>
@@ -87216,7 +87211,7 @@
       </c>
       <c r="AO620" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP620" t="inlineStr">
@@ -87224,52 +87219,48 @@
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS620" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_210</t>
-        </is>
-      </c>
+      <c r="AS620" t="inlineStr"/>
       <c r="AT620" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV620" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW620" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX620" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY620" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ620" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA620" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB620" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC620" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -87301,12 +87292,12 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -87340,17 +87331,17 @@
         </is>
       </c>
       <c r="N621" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O621" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R621" t="n">
-        <v>0</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="U621" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AA621" t="inlineStr">
@@ -87370,7 +87361,7 @@
       </c>
       <c r="AS621" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_306_MONTHLY</t>
+          <t>SER_FI_THL_TTR_210</t>
         </is>
       </c>
       <c r="AT621" t="n">
@@ -87378,42 +87369,42 @@
       </c>
       <c r="AV621" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW621" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX621" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY621" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ621" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA621" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB621" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC621" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -87445,12 +87436,12 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -87475,7 +87466,7 @@
       </c>
       <c r="L622" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="M622" t="inlineStr">
@@ -87484,22 +87475,22 @@
         </is>
       </c>
       <c r="N622" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O622" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R622" t="n">
-        <v>0.005977696639977366</v>
+        <v>0</v>
       </c>
       <c r="U622" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AA622" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO622" t="inlineStr">
@@ -87514,7 +87505,7 @@
       </c>
       <c r="AS622" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>SER_NO_FHI_306_MONTHLY</t>
         </is>
       </c>
       <c r="AT622" t="n">
@@ -87522,42 +87513,42 @@
       </c>
       <c r="AV622" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW622" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX622" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY622" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ622" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA622" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB622" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC622" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -87589,12 +87580,12 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>DE-BW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>Baden-Württemberg, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -87628,10 +87619,13 @@
         </is>
       </c>
       <c r="N623" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O623" t="n">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="R623" t="n">
+        <v>0.005977696639977366</v>
       </c>
       <c r="U623" t="inlineStr">
         <is>
@@ -87673,12 +87667,12 @@
       </c>
       <c r="AX623" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY623" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ623" t="inlineStr">
@@ -87693,12 +87687,12 @@
       </c>
       <c r="BB623" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC623" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -87730,12 +87724,12 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>DE-BW</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Baden-Württemberg, Germany</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -87871,12 +87865,12 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -88012,12 +88006,12 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>DE-SH</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Schleswig-Holstein, Germany</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -88153,12 +88147,12 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>DE-SN</t>
+          <t>DE-SH</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Sachsen, Germany</t>
+          <t>Schleswig-Holstein, Germany</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -88294,12 +88288,12 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>US-WY</t>
+          <t>DE-SN</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Wyoming, United States</t>
+          <t>Sachsen, Germany</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -88324,7 +88318,7 @@
       </c>
       <c r="L628" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="M628" t="inlineStr">
@@ -88338,17 +88332,14 @@
       <c r="O628" t="n">
         <v>1</v>
       </c>
-      <c r="P628" t="n">
-        <v>1</v>
-      </c>
       <c r="U628" t="inlineStr">
         <is>
-          <t>HOLD_US_dffcc011bc6b581b3682cb3dd210</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AA628" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AO628" t="inlineStr">
@@ -88363,7 +88354,7 @@
       </c>
       <c r="AS628" t="inlineStr">
         <is>
-          <t>HOLD_US_dffcc011bc6b581b3682cb3dd210</t>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
       <c r="AT628" t="n">
@@ -88371,17 +88362,17 @@
       </c>
       <c r="AV628" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="AW628" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="AX628" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="AY628" t="inlineStr">
@@ -88391,17 +88382,17 @@
       </c>
       <c r="AZ628" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>rki_survstat</t>
         </is>
       </c>
       <c r="BA628" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
       <c r="BB628" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
         </is>
       </c>
       <c r="BC628" t="inlineStr">
@@ -88438,12 +88429,12 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US-WY</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Wyoming, United States</t>
         </is>
       </c>
       <c r="H629" t="inlineStr">
@@ -88468,7 +88459,7 @@
       </c>
       <c r="L629" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="M629" t="inlineStr">
@@ -88477,22 +88468,22 @@
         </is>
       </c>
       <c r="N629" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O629" t="n">
-        <v>12</v>
-      </c>
-      <c r="R629" t="n">
-        <v>0.01434647193594568</v>
+        <v>1</v>
+      </c>
+      <c r="P629" t="n">
+        <v>1</v>
       </c>
       <c r="U629" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_US_dffcc011bc6b581b3682cb3dd210</t>
         </is>
       </c>
       <c r="AA629" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO629" t="inlineStr">
@@ -88507,7 +88498,7 @@
       </c>
       <c r="AS629" t="inlineStr">
         <is>
-          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+          <t>HOLD_US_dffcc011bc6b581b3682cb3dd210</t>
         </is>
       </c>
       <c r="AT629" t="n">
@@ -88515,42 +88506,42 @@
       </c>
       <c r="AV629" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW629" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX629" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="AY629" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ629" t="inlineStr">
         <is>
-          <t>rki_survstat</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="BA629" t="inlineStr">
         <is>
-          <t>Germany RKI SurvStat 2.0</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="BB629" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+          <t>https://data.cdc.gov/NNDSS/NNDSS-Weekly-Data/x9gk-5huc</t>
         </is>
       </c>
       <c r="BC629" t="inlineStr">
         <is>
-          <t>official_webforms_csv_export</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -88582,12 +88573,12 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>DE-BY</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>Bayern, Germany</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -88621,10 +88612,13 @@
         </is>
       </c>
       <c r="N630" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O630" t="n">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="R630" t="n">
+        <v>0.01434647193594568</v>
       </c>
       <c r="U630" t="inlineStr">
         <is>
@@ -88666,12 +88660,12 @@
       </c>
       <c r="AX630" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="AY630" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
       <c r="AZ630" t="inlineStr">
@@ -88686,12 +88680,12 @@
       </c>
       <c r="BB630" t="inlineStr">
         <is>
-          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
       <c r="BC630" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -88723,12 +88717,12 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>DE-HE</t>
+          <t>DE-BY</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Hessen, Germany</t>
+          <t>Bayern, Germany</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -88864,12 +88858,12 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>DE-NI</t>
+          <t>DE-HE</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>Niedersachsen, Germany</t>
+          <t>Hessen, Germany</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -89005,12 +88999,12 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>DE-NW</t>
+          <t>DE-NI</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Nordrhein-Westfalen, Germany</t>
+          <t>Niedersachsen, Germany</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -89146,12 +89140,12 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>DE-RP</t>
+          <t>DE-NW</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Rheinland-Pfalz, Germany</t>
+          <t>Nordrhein-Westfalen, Germany</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -89287,12 +89281,12 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>DE-TH</t>
+          <t>DE-RP</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Thüringen, Germany</t>
+          <t>Rheinland-Pfalz, Germany</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -89428,117 +89422,258 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
+          <t>DE-TH</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>Thüringen, Germany</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N636" t="n">
+        <v>1</v>
+      </c>
+      <c r="O636" t="n">
+        <v>1</v>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+        </is>
+      </c>
+      <c r="AA636" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO636" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP636" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS636" t="inlineStr">
+        <is>
+          <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
+        </is>
+      </c>
+      <c r="AT636" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV636" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW636" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX636" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="AY636" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ636" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA636" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB636" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Main.aspx</t>
+        </is>
+      </c>
+      <c r="BC636" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>listeriosis</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="G636" t="inlineStr">
+      <c r="G637" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr">
-        <is>
-          <t>D108</t>
-        </is>
-      </c>
-      <c r="I636" t="inlineStr">
-        <is>
-          <t>Listeriosis</t>
-        </is>
-      </c>
-      <c r="J636" t="inlineStr">
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
         <is>
           <t>李斯特菌病</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr">
+      <c r="K637" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L636" t="inlineStr">
+      <c r="L637" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="M636" t="inlineStr">
+      <c r="M637" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N636" t="n">
+      <c r="N637" t="n">
         <v>14</v>
       </c>
-      <c r="O636" t="n">
+      <c r="O637" t="n">
         <v>14</v>
       </c>
-      <c r="R636" t="n">
+      <c r="R637" t="n">
         <v>0.01673755059193663</v>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="U637" t="inlineStr">
         <is>
           <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
-      <c r="AA636" t="inlineStr">
+      <c r="AA637" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="AO636" t="inlineStr">
+      <c r="AO637" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP636" t="inlineStr">
+      <c r="AP637" t="inlineStr">
         <is>
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS636" t="inlineStr">
+      <c r="AS637" t="inlineStr">
         <is>
           <t>HOLD_DE_bcf77dd5c39d1691d1b7e1b96a96</t>
         </is>
       </c>
-      <c r="AT636" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV636" t="inlineStr">
+      <c r="AT637" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV637" t="inlineStr">
         <is>
           <t>rki_survstat</t>
         </is>
       </c>
-      <c r="AW636" t="inlineStr">
+      <c r="AW637" t="inlineStr">
         <is>
           <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
-      <c r="AX636" t="inlineStr">
+      <c r="AX637" t="inlineStr">
         <is>
           <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
-      <c r="AY636" t="inlineStr">
+      <c r="AY637" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
       </c>
-      <c r="AZ636" t="inlineStr">
+      <c r="AZ637" t="inlineStr">
         <is>
           <t>rki_survstat</t>
         </is>
       </c>
-      <c r="BA636" t="inlineStr">
+      <c r="BA637" t="inlineStr">
         <is>
           <t>Germany RKI SurvStat 2.0</t>
         </is>
       </c>
-      <c r="BB636" t="inlineStr">
+      <c r="BB637" t="inlineStr">
         <is>
           <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
         </is>
       </c>
-      <c r="BC636" t="inlineStr">
+      <c r="BC637" t="inlineStr">
         <is>
           <t>official_webforms_csv_export</t>
         </is>
@@ -89660,7 +89795,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="10">
@@ -89670,7 +89805,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="11">
@@ -89722,7 +89857,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1087</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="16">
